--- a/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -92,7 +92,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Enthaelt Alpha-ID-Codes der Versionen 2018 bis 2025</t>
+    <t>Enthaelt Alpha-ID-Codes der aller verfügbarer Versionen</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
+++ b/branches/develop/ValueSet-mii-vs-diagnose-alphaid.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
